--- a/RAGU LOS/ste/output/ste_ragu.xlsx
+++ b/RAGU LOS/ste/output/ste_ragu.xlsx
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -838,6 +838,11 @@
           <t>2026-09-06/2026-09-12</t>
         </is>
       </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>2026-09-13/2026-09-19</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -849,7 +854,7 @@
         <v>134.5604309856327</v>
       </c>
       <c r="C2" t="n">
-        <v>134.5779375050317</v>
+        <v>134.5779375050316</v>
       </c>
       <c r="D2" t="n">
         <v>134.7189061544075</v>
@@ -873,13 +878,13 @@
         <v>136.5189509248592</v>
       </c>
       <c r="K2" t="n">
-        <v>136.4676662974039</v>
+        <v>136.467666297404</v>
       </c>
       <c r="L2" t="n">
-        <v>135.6865522182397</v>
+        <v>135.6865522182398</v>
       </c>
       <c r="M2" t="n">
-        <v>136.9409994384725</v>
+        <v>136.939193134382</v>
       </c>
       <c r="N2" t="n">
         <v>136.2926431673899</v>
@@ -909,25 +914,28 @@
         <v>137.0004567979578</v>
       </c>
       <c r="W2" t="n">
-        <v>137.7418398721138</v>
+        <v>137.7202308735054</v>
       </c>
       <c r="X2" t="n">
-        <v>137.3346841078638</v>
+        <v>137.3392893270023</v>
       </c>
       <c r="Y2" t="n">
-        <v>137.9265713056258</v>
+        <v>137.8644752992943</v>
       </c>
       <c r="Z2" t="n">
-        <v>137.3366536684743</v>
+        <v>137.3608071623642</v>
       </c>
       <c r="AA2" t="n">
-        <v>137.2557304359934</v>
+        <v>137.519419922114</v>
       </c>
       <c r="AB2" t="n">
-        <v>138.1324747011026</v>
+        <v>137.5949343504855</v>
       </c>
       <c r="AC2" t="n">
-        <v>139.7327398234332</v>
+        <v>137.2765830338531</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>137.4612039372404</v>
       </c>
     </row>
     <row r="3">
@@ -1000,25 +1008,28 @@
         <v>-0.1250414382457734</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3838582886019992</v>
+        <v>-0.3823031788418234</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2532699824754161</v>
+        <v>-0.254436116627005</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.296067916969406</v>
+        <v>-0.2855456133790426</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1354024599938555</v>
+        <v>0.0753509679117883</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.06936151591241924</v>
+        <v>-0.1860743828638363</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.2639604748292186</v>
+        <v>-0.3108766397042473</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.402482840218426</v>
+        <v>0.03230159002629307</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.2332315850964051</v>
       </c>
     </row>
     <row r="4">
@@ -1028,88 +1039,91 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.137189851433196</v>
+        <v>1.259543259622068</v>
       </c>
       <c r="C4" t="n">
-        <v>1.324052397175176</v>
+        <v>1.359794043021511</v>
       </c>
       <c r="D4" t="n">
-        <v>1.541919205680379</v>
+        <v>1.667662658300501</v>
       </c>
       <c r="E4" t="n">
-        <v>1.96832709461436</v>
+        <v>1.900567885434507</v>
       </c>
       <c r="F4" t="n">
-        <v>2.488802320637977</v>
+        <v>2.414305081406356</v>
       </c>
       <c r="G4" t="n">
-        <v>2.429733392221895</v>
+        <v>2.38276335066755</v>
       </c>
       <c r="H4" t="n">
         <v>2.87207162237852</v>
       </c>
       <c r="I4" t="n">
-        <v>2.614869504083093</v>
+        <v>2.614869504083102</v>
       </c>
       <c r="J4" t="n">
-        <v>3.812609316566867</v>
+        <v>3.812609316566847</v>
       </c>
       <c r="K4" t="n">
-        <v>3.707292408489875</v>
+        <v>3.707292408489872</v>
       </c>
       <c r="L4" t="n">
-        <v>3.444319708257608</v>
+        <v>3.44665191074496</v>
       </c>
       <c r="M4" t="n">
-        <v>3.567078614316504</v>
+        <v>3.567126338645887</v>
       </c>
       <c r="N4" t="n">
-        <v>4.496487758462105</v>
+        <v>4.496235065421107</v>
       </c>
       <c r="O4" t="n">
-        <v>3.929905831330622</v>
+        <v>3.94435125067836</v>
       </c>
       <c r="P4" t="n">
-        <v>4.21377551862552</v>
+        <v>4.213775518625501</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.837410406095596</v>
+        <v>3.880589075897163</v>
       </c>
       <c r="R4" t="n">
-        <v>4.872410053668847</v>
+        <v>4.881215806047438</v>
       </c>
       <c r="S4" t="n">
-        <v>4.321531094403529</v>
+        <v>4.32153109440354</v>
       </c>
       <c r="T4" t="n">
         <v>4.065381870530694</v>
       </c>
       <c r="U4" t="n">
-        <v>3.993844587495262</v>
+        <v>4.004049102898515</v>
       </c>
       <c r="V4" t="n">
         <v>3.143937785230215</v>
       </c>
       <c r="W4" t="n">
-        <v>3.453921311648024</v>
+        <v>3.464262073744603</v>
       </c>
       <c r="X4" t="n">
-        <v>3.077275894658347</v>
+        <v>3.023998439548365</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.540541558798227</v>
+        <v>3.651022520697587</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.517460330624128</v>
+        <v>3.512872178819046</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.503089607823755</v>
+        <v>3.800442938811831</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.846649799894099</v>
+        <v>3.356430714703734</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.552373210657755</v>
+        <v>3.026996324036509</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.688342662641205</v>
       </c>
     </row>
     <row r="5">
@@ -1122,16 +1136,16 @@
         <v>5.644519355697938</v>
       </c>
       <c r="C5" t="n">
-        <v>5.417109523204974</v>
+        <v>5.417109523204971</v>
       </c>
       <c r="D5" t="n">
         <v>5.336899838516342</v>
       </c>
       <c r="E5" t="n">
-        <v>5.818572209781549</v>
+        <v>5.818572209781546</v>
       </c>
       <c r="F5" t="n">
-        <v>5.906341523563954</v>
+        <v>5.906341523563946</v>
       </c>
       <c r="G5" t="n">
         <v>5.672823464806111</v>
@@ -1143,13 +1157,13 @@
         <v>6.3540035274861</v>
       </c>
       <c r="J5" t="n">
-        <v>6.46565272720238</v>
+        <v>6.465652727202383</v>
       </c>
       <c r="K5" t="n">
         <v>6.439216388517878</v>
       </c>
       <c r="L5" t="n">
-        <v>6.355294679366496</v>
+        <v>6.3552946793665</v>
       </c>
       <c r="M5" t="n">
         <v>6.355292696404416</v>
@@ -1161,19 +1175,19 @@
         <v>6.244339946715268</v>
       </c>
       <c r="P5" t="n">
-        <v>6.242989180681812</v>
+        <v>6.242989180681817</v>
       </c>
       <c r="Q5" t="n">
         <v>5.967034713487968</v>
       </c>
       <c r="R5" t="n">
-        <v>6.104301383707485</v>
+        <v>6.10430138370748</v>
       </c>
       <c r="S5" t="n">
-        <v>6.814489133058596</v>
+        <v>6.8144891330586</v>
       </c>
       <c r="T5" t="n">
-        <v>6.030332687329206</v>
+        <v>6.030332687329194</v>
       </c>
       <c r="U5" t="n">
         <v>6.567728111418498</v>
@@ -1182,25 +1196,28 @@
         <v>6.341203609470618</v>
       </c>
       <c r="W5" t="n">
-        <v>6.080248207156369</v>
+        <v>6.080086661123241</v>
       </c>
       <c r="X5" t="n">
-        <v>5.687084399965505</v>
+        <v>5.691283522854956</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.452355819388647</v>
+        <v>6.379082733677587</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.253028723196672</v>
+        <v>6.232371287139952</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.228435857076527</v>
+        <v>6.281127619979269</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.248670152868404</v>
+        <v>5.890733679950617</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.741668088370131</v>
+        <v>5.7303922074188</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>6.431757844854843</v>
       </c>
     </row>
     <row r="6">
@@ -1219,10 +1236,10 @@
         <v>1.787805777167024</v>
       </c>
       <c r="E6" t="n">
-        <v>1.791244046291854</v>
+        <v>1.791244046291852</v>
       </c>
       <c r="F6" t="n">
-        <v>1.694380991794105</v>
+        <v>1.694380991794107</v>
       </c>
       <c r="G6" t="n">
         <v>1.667278357832026</v>
@@ -1240,16 +1257,16 @@
         <v>1.971307930380207</v>
       </c>
       <c r="L6" t="n">
-        <v>1.599976535332509</v>
+        <v>1.599976535332507</v>
       </c>
       <c r="M6" t="n">
         <v>2.004076609729814</v>
       </c>
       <c r="N6" t="n">
-        <v>2.037796780453785</v>
+        <v>2.037796780453788</v>
       </c>
       <c r="O6" t="n">
-        <v>1.860600213168589</v>
+        <v>1.860600213168585</v>
       </c>
       <c r="P6" t="n">
         <v>1.782460024726733</v>
@@ -1261,37 +1278,40 @@
         <v>2.140831858930341</v>
       </c>
       <c r="S6" t="n">
-        <v>2.193812629762512</v>
+        <v>2.193812629762514</v>
       </c>
       <c r="T6" t="n">
-        <v>1.879607243516972</v>
+        <v>1.879607243516966</v>
       </c>
       <c r="U6" t="n">
-        <v>1.724231727553022</v>
+        <v>1.724231727553024</v>
       </c>
       <c r="V6" t="n">
         <v>1.662185175931949</v>
       </c>
       <c r="W6" t="n">
-        <v>2.041328938217708</v>
+        <v>2.033012048912933</v>
       </c>
       <c r="X6" t="n">
-        <v>1.599717660159135</v>
+        <v>1.595923885425469</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.924523695987059</v>
+        <v>1.902741439923062</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.706101780086671</v>
+        <v>1.730944541637672</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.577816392675569</v>
+        <v>1.748502670054186</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.906826776517307</v>
+        <v>1.80023728994588</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.814535869371221</v>
+        <v>1.429040339866881</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.733658648787693</v>
       </c>
     </row>
     <row r="7">
@@ -1301,22 +1321,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>143.0506677811769</v>
+        <v>143.1730211893658</v>
       </c>
       <c r="C7" t="n">
-        <v>142.2979274289611</v>
+        <v>142.3336690748075</v>
       </c>
       <c r="D7" t="n">
-        <v>142.7420580279242</v>
+        <v>142.8678014805443</v>
       </c>
       <c r="E7" t="n">
-        <v>144.129401048052</v>
+        <v>144.0616418388722</v>
       </c>
       <c r="F7" t="n">
-        <v>144.8051295239788</v>
+        <v>144.7306322847472</v>
       </c>
       <c r="G7" t="n">
-        <v>144.9612031216329</v>
+        <v>144.9142330800786</v>
       </c>
       <c r="H7" t="n">
         <v>145.0576354891677</v>
@@ -1328,61 +1348,64 @@
         <v>148.27817405507</v>
       </c>
       <c r="K7" t="n">
-        <v>148.2155600439258</v>
+        <v>148.2155600439256</v>
       </c>
       <c r="L7" t="n">
-        <v>146.6868913361453</v>
+        <v>146.6892235386327</v>
       </c>
       <c r="M7" t="n">
-        <v>147.963064241569</v>
+        <v>147.9649320144552</v>
       </c>
       <c r="N7" t="n">
-        <v>148.9908800130118</v>
+        <v>148.9906273199708</v>
       </c>
       <c r="O7" t="n">
-        <v>147.6933842919227</v>
+        <v>147.7078297112704</v>
       </c>
       <c r="P7" t="n">
         <v>148.2359152544169</v>
       </c>
       <c r="Q7" t="n">
-        <v>147.7141367853364</v>
+        <v>147.757315455138</v>
       </c>
       <c r="R7" t="n">
-        <v>149.7440319601797</v>
+        <v>149.7528377125583</v>
       </c>
       <c r="S7" t="n">
-        <v>150.77242723766</v>
+        <v>150.7724272376601</v>
       </c>
       <c r="T7" t="n">
         <v>148.7656649372706</v>
       </c>
       <c r="U7" t="n">
-        <v>149.2382493247338</v>
+        <v>149.248453840137</v>
       </c>
       <c r="V7" t="n">
         <v>147.9610744093644</v>
       </c>
       <c r="W7" t="n">
-        <v>148.9662512900719</v>
+        <v>148.9475309016474</v>
       </c>
       <c r="X7" t="n">
-        <v>147.5775743666058</v>
+        <v>147.5269257228695</v>
       </c>
       <c r="Y7" t="n">
-        <v>149.520120142167</v>
+        <v>149.4709550762326</v>
       </c>
       <c r="Z7" t="n">
-        <v>148.8877131558419</v>
+        <v>148.8994051025361</v>
       </c>
       <c r="AA7" t="n">
-        <v>148.56571140703</v>
+        <v>149.1671272255782</v>
       </c>
       <c r="AB7" t="n">
-        <v>149.9653903504092</v>
+        <v>148.2947186624033</v>
       </c>
       <c r="AC7" t="n">
-        <v>152.2437998320508</v>
+        <v>147.662966257221</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>147.397140312131</v>
       </c>
     </row>
     <row r="8">
@@ -1455,25 +1478,28 @@
         <v>14445556.33</v>
       </c>
       <c r="W8" t="n">
-        <v>14560323.08</v>
+        <v>14590541.69</v>
       </c>
       <c r="X8" t="n">
-        <v>13747310</v>
+        <v>13867492.61</v>
       </c>
       <c r="Y8" t="n">
-        <v>12524015.11</v>
+        <v>12990570.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>11663470.45</v>
+        <v>12604081.71</v>
       </c>
       <c r="AA8" t="n">
-        <v>10271160.04</v>
+        <v>13805307.74</v>
       </c>
       <c r="AB8" t="n">
-        <v>4773605.870000001</v>
+        <v>11062219.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>359639.24</v>
+        <v>9761064.550000001</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>4116371.66</v>
       </c>
     </row>
     <row r="9">
@@ -1486,7 +1512,7 @@
         <v>1.45642305239309</v>
       </c>
       <c r="C9" t="n">
-        <v>1.471197701285301</v>
+        <v>1.471197701285302</v>
       </c>
       <c r="D9" t="n">
         <v>1.476480632425605</v>
@@ -1531,10 +1557,10 @@
         <v>1.435971182672166</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42743982829347</v>
+        <v>1.427439828293471</v>
       </c>
       <c r="S9" t="n">
-        <v>1.384871193991649</v>
+        <v>1.384871193991648</v>
       </c>
       <c r="T9" t="n">
         <v>1.432024471715291</v>
@@ -1546,25 +1572,28 @@
         <v>1.412951986187142</v>
       </c>
       <c r="W9" t="n">
-        <v>1.428927440640524</v>
+        <v>1.428937442230338</v>
       </c>
       <c r="X9" t="n">
-        <v>1.453690541216047</v>
+        <v>1.45342152931905</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.406255314134992</v>
+        <v>1.410662701171431</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.418309863742607</v>
+        <v>1.419570976736918</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.419811484635659</v>
+        <v>1.416598050504109</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.418575762963842</v>
+        <v>1.440757664700206</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.450201448365419</v>
+        <v>1.45092085077335</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.407491500141197</v>
       </c>
     </row>
     <row r="10">
@@ -1610,10 +1639,10 @@
         <v>0.2213703341467169</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2208886174220888</v>
+        <v>0.2208886174220887</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2234199969547344</v>
+        <v>0.2234199969547345</v>
       </c>
       <c r="P10" t="n">
         <v>0.2245362853610467</v>
@@ -1625,37 +1654,40 @@
         <v>0.2194166877295665</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2186598195748213</v>
+        <v>0.2186598195748212</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2231484679497575</v>
+        <v>0.2231484679497576</v>
       </c>
       <c r="U10" t="n">
-        <v>0.225368118177814</v>
+        <v>0.2253681181778139</v>
       </c>
       <c r="V10" t="n">
         <v>0.2262544974866864</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2208381580254613</v>
+        <v>0.2209569707298152</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2271468905691552</v>
+        <v>0.2272010873510647</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.222506804343042</v>
+        <v>0.2228179794296705</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.2256271174273333</v>
+        <v>0.2252722208337475</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.2274597658189204</v>
+        <v>0.2250213904277973</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2227596174783242</v>
+        <v>0.2242823244293446</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.2240780590089826</v>
+        <v>0.2295851380019017</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.2252334478744615</v>
       </c>
     </row>
   </sheetData>

--- a/RAGU LOS/ste/output/ste_ragu.xlsx
+++ b/RAGU LOS/ste/output/ste_ragu.xlsx
@@ -3,11 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="14685" yWindow="-21720" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-23820" yWindow="-21720" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Tables (M)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Tables (W)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Tables (M) w_cb_zip" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Tables (M) no zip" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Tables (W)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -46,8 +48,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -413,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -424,32 +427,57 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>2025 M11</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2025 M12</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>2026 M01</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2026 M02</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>2026 M03</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>2026 M04</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>2026 M05</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>2026 M06</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>2026 M07</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>2026 M08</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2026 M09</t>
         </is>
       </c>
     </row>
@@ -460,22 +488,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>134.3934425718513</v>
+        <v>131.3651561126205</v>
       </c>
       <c r="C2" t="n">
+        <v>131.6513915440997</v>
+      </c>
+      <c r="D2" t="n">
+        <v>132.2504477975082</v>
+      </c>
+      <c r="E2" t="n">
+        <v>133.1113250892619</v>
+      </c>
+      <c r="F2" t="n">
+        <v>134.3934425718512</v>
+      </c>
+      <c r="G2" t="n">
         <v>135.0739193974012</v>
       </c>
-      <c r="D2" t="n">
+      <c r="H2" t="n">
         <v>136.244090882718</v>
       </c>
-      <c r="E2" t="n">
+      <c r="I2" t="n">
         <v>136.5269757194134</v>
       </c>
-      <c r="F2" t="n">
-        <v>137.3371379047234</v>
-      </c>
-      <c r="G2" t="n">
-        <v>137.5280812563184</v>
+      <c r="J2" t="n">
+        <v>137.3586655760463</v>
+      </c>
+      <c r="K2" t="n">
+        <v>137.5708487630104</v>
+      </c>
+      <c r="L2" t="n">
+        <v>137.3436104271622</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +528,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.3569382769190383</v>
+        <v>-0.1294456775458741</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.2714591654647336</v>
+        <v>-0.01036125741728711</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3960304401416579</v>
+        <v>0.05402914064546849</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5679373861838997</v>
+        <v>-0.01788117065970596</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5085678215595806</v>
+        <v>0.07112380814493235</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4507806287642211</v>
+        <v>0.1946555925854909</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1045146632951344</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.07138401696630581</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.01281365682680757</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.3435312075026786</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.5638240054918526</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +568,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.283707170891394</v>
+        <v>2.142798503461352</v>
       </c>
       <c r="C4" t="n">
-        <v>2.323347173394712</v>
+        <v>1.914371261521075</v>
       </c>
       <c r="D4" t="n">
-        <v>3.413349144141401</v>
+        <v>2.119307232197779</v>
       </c>
       <c r="E4" t="n">
-        <v>3.998282604584596</v>
+        <v>1.115884742822912</v>
       </c>
       <c r="F4" t="n">
-        <v>4.373069717223825</v>
+        <v>1.095483786418988</v>
       </c>
       <c r="G4" t="n">
-        <v>4.373994647581875</v>
+        <v>2.317275251588041</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.474837500958335</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.053175414960784</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.227849958639407</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.530698325425688</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.096963395084881</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +608,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.567109301789449</v>
+        <v>4.350490189058533</v>
       </c>
       <c r="C5" t="n">
+        <v>3.959938585961525</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.432585076535629</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.977841807911377</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.567109301789445</v>
+      </c>
+      <c r="G5" t="n">
         <v>5.801014611287784</v>
       </c>
-      <c r="D5" t="n">
+      <c r="H5" t="n">
         <v>6.423008339670849</v>
       </c>
-      <c r="E5" t="n">
+      <c r="I5" t="n">
         <v>6.169638525131881</v>
       </c>
-      <c r="F5" t="n">
-        <v>6.367450541489774</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5.804736781086261</v>
+      <c r="J5" t="n">
+        <v>6.378209781427979</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.188021541263446</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.889268950056255</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +648,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.504650371042686</v>
+        <v>1.115541807286742</v>
       </c>
       <c r="C6" t="n">
-        <v>1.672336970547683</v>
+        <v>1.091532106112449</v>
       </c>
       <c r="D6" t="n">
-        <v>1.783094257537567</v>
+        <v>1.087923896687248</v>
       </c>
       <c r="E6" t="n">
-        <v>1.882743456143123</v>
+        <v>1.175085726381635</v>
       </c>
       <c r="F6" t="n">
-        <v>2.04867878927317</v>
+        <v>1.504650371042688</v>
       </c>
       <c r="G6" t="n">
-        <v>1.909205044092916</v>
+        <v>1.672336970547677</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.783094257537565</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.882743456143129</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.979285459538064</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.815405934441572</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.665868262722071</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +688,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>142.3957119228214</v>
+        <v>138.8445409348813</v>
       </c>
       <c r="C7" t="n">
-        <v>144.5992660948387</v>
+        <v>138.6068722402775</v>
       </c>
       <c r="D7" t="n">
-        <v>147.4670704461417</v>
+        <v>139.9442931435743</v>
       </c>
       <c r="E7" t="n">
-        <v>148.0097029190891</v>
+        <v>140.3622561957181</v>
       </c>
       <c r="F7" t="n">
-        <v>149.6191516521196</v>
+        <v>142.635550623413</v>
       </c>
       <c r="G7" t="n">
-        <v>150.1832987948843</v>
+        <v>145.0593089310823</v>
+      </c>
+      <c r="H7" t="n">
+        <v>148.0291039063954</v>
+      </c>
+      <c r="I7" t="n">
+        <v>148.5611490986829</v>
+      </c>
+      <c r="J7" t="n">
+        <v>149.957942860205</v>
+      </c>
+      <c r="K7" t="n">
+        <v>149.4485057716438</v>
+      </c>
+      <c r="L7" t="n">
+        <v>148.5543127717034</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +728,37 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>46957669.38</v>
+      </c>
+      <c r="C8" t="n">
+        <v>48436705.36</v>
+      </c>
+      <c r="D8" t="n">
+        <v>41847911.84</v>
+      </c>
+      <c r="E8" t="n">
+        <v>51674677.01000001</v>
+      </c>
+      <c r="F8" t="n">
         <v>107724085.98</v>
       </c>
-      <c r="C8" t="n">
+      <c r="G8" t="n">
         <v>90227374.95</v>
       </c>
-      <c r="D8" t="n">
+      <c r="H8" t="n">
         <v>72604977.90000001</v>
       </c>
-      <c r="E8" t="n">
+      <c r="I8" t="n">
         <v>82073268.25</v>
       </c>
-      <c r="F8" t="n">
-        <v>58437607.40000001</v>
-      </c>
-      <c r="G8" t="n">
-        <v>5978628.67</v>
+      <c r="J8" t="n">
+        <v>72933369.03999999</v>
+      </c>
+      <c r="K8" t="n">
+        <v>57974773.56</v>
+      </c>
+      <c r="L8" t="n">
+        <v>54925118.76</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +768,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.461418897695721</v>
+        <v>1.54469521345703</v>
       </c>
       <c r="C9" t="n">
+        <v>1.573477892825947</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.538778447967365</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.50060230154756</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.461418897695722</v>
+      </c>
+      <c r="G9" t="n">
         <v>1.44642686135875</v>
       </c>
-      <c r="D9" t="n">
+      <c r="H9" t="n">
         <v>1.408017259001815</v>
       </c>
-      <c r="E9" t="n">
+      <c r="I9" t="n">
         <v>1.423414524323585</v>
       </c>
-      <c r="F9" t="n">
-        <v>1.411364921536596</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.446190776793042</v>
+      <c r="J9" t="n">
+        <v>1.410715375913849</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.4222860687494</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.440849861651826</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +808,37 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>0.2340636884673322</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2344066841983936</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.234458230047325</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.2332130610516909</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.2285049946993902</v>
       </c>
-      <c r="C10" t="n">
-        <v>0.2261094718493188</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="G10" t="n">
+        <v>0.2261094718493189</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.2245272248923205</v>
       </c>
-      <c r="E10" t="n">
-        <v>0.2231036649122411</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.2207331601532404</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.2227256422272441</v>
+      <c r="I10" t="n">
+        <v>0.223103664912241</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.2217244934351705</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2240656295079775</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2262018819611133</v>
       </c>
     </row>
   </sheetData>
@@ -689,7 +852,916 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>STE</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2025 M11</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2025 M12</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>2026 M01</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2026 M02</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>2026 M03</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2026 M04</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>2026 M05</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>2026 M06</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>2026 M07</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2026 M08</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2026 M09</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Model Score</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>131.3651561126205</v>
+      </c>
+      <c r="C2" t="n">
+        <v>131.6513915440997</v>
+      </c>
+      <c r="D2" t="n">
+        <v>132.2504477975082</v>
+      </c>
+      <c r="E2" t="n">
+        <v>133.1113250892619</v>
+      </c>
+      <c r="F2" t="n">
+        <v>134.3934425718512</v>
+      </c>
+      <c r="G2" t="n">
+        <v>135.0739193974012</v>
+      </c>
+      <c r="H2" t="n">
+        <v>136.244090882718</v>
+      </c>
+      <c r="I2" t="n">
+        <v>136.5269757194134</v>
+      </c>
+      <c r="J2" t="n">
+        <v>137.3586655760463</v>
+      </c>
+      <c r="K2" t="n">
+        <v>137.5708487630104</v>
+      </c>
+      <c r="L2" t="n">
+        <v>137.3436104271622</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Expected Gross Loss Impact</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-0.4229003424688358</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.4428318907520463</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.3765087740779052</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.3989915474939778</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.3569382769190383</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.2714591654647336</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.3960304401416579</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.5679373861838997</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.4859732772138159</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.1584695948813817</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.001594424095856084</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Recovery Impact</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.138007016336803</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.908082117854356</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.112410699763467</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.11268942949778</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.091996458559675</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.309290282883682</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.462081092307393</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.038426162964447</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.212499034551448</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.517846776568211</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.084337024514781</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LTV Impact</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4.350490189058533</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.959938585961525</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.432585076535629</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.977841807911377</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.567109301789445</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.801014611287784</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6.423008339670849</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6.169638525131881</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6.378209781427979</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.188021541263446</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.889268950056255</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>APR Impact</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.115541807286742</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.091532106112449</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.087923896687248</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.175085726381635</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.504650371042688</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.672336970547677</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.783094257537565</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.882743456143129</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.979285459538064</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.815405934441572</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.665868262722071</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RAGU Score</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>138.5462947828338</v>
+      </c>
+      <c r="C7" t="n">
+        <v>138.168112463276</v>
+      </c>
+      <c r="D7" t="n">
+        <v>139.5068586964166</v>
+      </c>
+      <c r="E7" t="n">
+        <v>139.9779505055587</v>
+      </c>
+      <c r="F7" t="n">
+        <v>142.2040012104897</v>
+      </c>
+      <c r="G7" t="n">
+        <v>144.5852092043276</v>
+      </c>
+      <c r="H7" t="n">
+        <v>147.5158023943077</v>
+      </c>
+      <c r="I7" t="n">
+        <v>148.049846477469</v>
+      </c>
+      <c r="J7" t="n">
+        <v>149.4438050020764</v>
+      </c>
+      <c r="K7" t="n">
+        <v>148.9336534204023</v>
+      </c>
+      <c r="L7" t="n">
+        <v>147.9794568197373</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Amount Financed</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>46957669.38</v>
+      </c>
+      <c r="C8" t="n">
+        <v>48436705.36</v>
+      </c>
+      <c r="D8" t="n">
+        <v>41847911.84</v>
+      </c>
+      <c r="E8" t="n">
+        <v>51674677.01000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>107724085.98</v>
+      </c>
+      <c r="G8" t="n">
+        <v>90227374.95</v>
+      </c>
+      <c r="H8" t="n">
+        <v>72604977.90000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>82073268.25</v>
+      </c>
+      <c r="J8" t="n">
+        <v>72933369.03999999</v>
+      </c>
+      <c r="K8" t="n">
+        <v>57974773.56</v>
+      </c>
+      <c r="L8" t="n">
+        <v>54925118.76</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Weighted LTV</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.54469521345703</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.573477892825947</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.538778447967365</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.50060230154756</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.461418897695722</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.44642686135875</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.408017259001815</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.423414524323585</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.410715375913849</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.4222860687494</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.440849861651826</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Weighted APR</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.2340636884673322</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2344066841983936</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.234458230047325</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.2332130610516909</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2285049946993902</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.2261094718493189</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.2245272248923205</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.223103664912241</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.2217244934351705</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2240656295079775</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2262018819611133</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12">
+        <f>'Data Tables (M) w_cb_zip'!B2-'Data Tables (M) no zip'!B2</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>'Data Tables (M) w_cb_zip'!C2-'Data Tables (M) no zip'!C2</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>'Data Tables (M) w_cb_zip'!D2-'Data Tables (M) no zip'!D2</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>'Data Tables (M) w_cb_zip'!E2-'Data Tables (M) no zip'!E2</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>'Data Tables (M) w_cb_zip'!F2-'Data Tables (M) no zip'!F2</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>'Data Tables (M) w_cb_zip'!G2-'Data Tables (M) no zip'!G2</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>'Data Tables (M) w_cb_zip'!H2-'Data Tables (M) no zip'!H2</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>'Data Tables (M) w_cb_zip'!I2-'Data Tables (M) no zip'!I2</f>
+        <v/>
+      </c>
+      <c r="J12">
+        <f>'Data Tables (M) w_cb_zip'!J2-'Data Tables (M) no zip'!J2</f>
+        <v/>
+      </c>
+      <c r="K12">
+        <f>'Data Tables (M) w_cb_zip'!K2-'Data Tables (M) no zip'!K2</f>
+        <v/>
+      </c>
+      <c r="L12">
+        <f>'Data Tables (M) w_cb_zip'!L2-'Data Tables (M) no zip'!L2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="1">
+        <f>'Data Tables (M) w_cb_zip'!B3-'Data Tables (M) no zip'!B3</f>
+        <v/>
+      </c>
+      <c r="C13" s="1">
+        <f>'Data Tables (M) w_cb_zip'!C3-'Data Tables (M) no zip'!C3</f>
+        <v/>
+      </c>
+      <c r="D13" s="1">
+        <f>'Data Tables (M) w_cb_zip'!D3-'Data Tables (M) no zip'!D3</f>
+        <v/>
+      </c>
+      <c r="E13" s="1">
+        <f>'Data Tables (M) w_cb_zip'!E3-'Data Tables (M) no zip'!E3</f>
+        <v/>
+      </c>
+      <c r="F13" s="1">
+        <f>'Data Tables (M) w_cb_zip'!F3-'Data Tables (M) no zip'!F3</f>
+        <v/>
+      </c>
+      <c r="G13" s="1">
+        <f>'Data Tables (M) w_cb_zip'!G3-'Data Tables (M) no zip'!G3</f>
+        <v/>
+      </c>
+      <c r="H13" s="1">
+        <f>'Data Tables (M) w_cb_zip'!H3-'Data Tables (M) no zip'!H3</f>
+        <v/>
+      </c>
+      <c r="I13" s="1">
+        <f>'Data Tables (M) w_cb_zip'!I3-'Data Tables (M) no zip'!I3</f>
+        <v/>
+      </c>
+      <c r="J13" s="1">
+        <f>'Data Tables (M) w_cb_zip'!J3-'Data Tables (M) no zip'!J3</f>
+        <v/>
+      </c>
+      <c r="K13" s="1">
+        <f>'Data Tables (M) w_cb_zip'!K3-'Data Tables (M) no zip'!K3</f>
+        <v/>
+      </c>
+      <c r="L13" s="1">
+        <f>'Data Tables (M) w_cb_zip'!L3-'Data Tables (M) no zip'!L3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14">
+        <f>'Data Tables (M) w_cb_zip'!B4-'Data Tables (M) no zip'!B4</f>
+        <v/>
+      </c>
+      <c r="C14">
+        <f>'Data Tables (M) w_cb_zip'!C4-'Data Tables (M) no zip'!C4</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>'Data Tables (M) w_cb_zip'!D4-'Data Tables (M) no zip'!D4</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>'Data Tables (M) w_cb_zip'!E4-'Data Tables (M) no zip'!E4</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>'Data Tables (M) w_cb_zip'!F4-'Data Tables (M) no zip'!F4</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>'Data Tables (M) w_cb_zip'!G4-'Data Tables (M) no zip'!G4</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>'Data Tables (M) w_cb_zip'!H4-'Data Tables (M) no zip'!H4</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>'Data Tables (M) w_cb_zip'!I4-'Data Tables (M) no zip'!I4</f>
+        <v/>
+      </c>
+      <c r="J14">
+        <f>'Data Tables (M) w_cb_zip'!J4-'Data Tables (M) no zip'!J4</f>
+        <v/>
+      </c>
+      <c r="K14">
+        <f>'Data Tables (M) w_cb_zip'!K4-'Data Tables (M) no zip'!K4</f>
+        <v/>
+      </c>
+      <c r="L14">
+        <f>'Data Tables (M) w_cb_zip'!L4-'Data Tables (M) no zip'!L4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15">
+        <f>'Data Tables (M) w_cb_zip'!B5-'Data Tables (M) no zip'!B5</f>
+        <v/>
+      </c>
+      <c r="C15">
+        <f>'Data Tables (M) w_cb_zip'!C5-'Data Tables (M) no zip'!C5</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>'Data Tables (M) w_cb_zip'!D5-'Data Tables (M) no zip'!D5</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>'Data Tables (M) w_cb_zip'!E5-'Data Tables (M) no zip'!E5</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>'Data Tables (M) w_cb_zip'!F5-'Data Tables (M) no zip'!F5</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>'Data Tables (M) w_cb_zip'!G5-'Data Tables (M) no zip'!G5</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>'Data Tables (M) w_cb_zip'!H5-'Data Tables (M) no zip'!H5</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>'Data Tables (M) w_cb_zip'!I5-'Data Tables (M) no zip'!I5</f>
+        <v/>
+      </c>
+      <c r="J15">
+        <f>'Data Tables (M) w_cb_zip'!J5-'Data Tables (M) no zip'!J5</f>
+        <v/>
+      </c>
+      <c r="K15">
+        <f>'Data Tables (M) w_cb_zip'!K5-'Data Tables (M) no zip'!K5</f>
+        <v/>
+      </c>
+      <c r="L15">
+        <f>'Data Tables (M) w_cb_zip'!L5-'Data Tables (M) no zip'!L5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16">
+        <f>'Data Tables (M) w_cb_zip'!B6-'Data Tables (M) no zip'!B6</f>
+        <v/>
+      </c>
+      <c r="C16">
+        <f>'Data Tables (M) w_cb_zip'!C6-'Data Tables (M) no zip'!C6</f>
+        <v/>
+      </c>
+      <c r="D16">
+        <f>'Data Tables (M) w_cb_zip'!D6-'Data Tables (M) no zip'!D6</f>
+        <v/>
+      </c>
+      <c r="E16">
+        <f>'Data Tables (M) w_cb_zip'!E6-'Data Tables (M) no zip'!E6</f>
+        <v/>
+      </c>
+      <c r="F16">
+        <f>'Data Tables (M) w_cb_zip'!F6-'Data Tables (M) no zip'!F6</f>
+        <v/>
+      </c>
+      <c r="G16">
+        <f>'Data Tables (M) w_cb_zip'!G6-'Data Tables (M) no zip'!G6</f>
+        <v/>
+      </c>
+      <c r="H16">
+        <f>'Data Tables (M) w_cb_zip'!H6-'Data Tables (M) no zip'!H6</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>'Data Tables (M) w_cb_zip'!I6-'Data Tables (M) no zip'!I6</f>
+        <v/>
+      </c>
+      <c r="J16">
+        <f>'Data Tables (M) w_cb_zip'!J6-'Data Tables (M) no zip'!J6</f>
+        <v/>
+      </c>
+      <c r="K16">
+        <f>'Data Tables (M) w_cb_zip'!K6-'Data Tables (M) no zip'!K6</f>
+        <v/>
+      </c>
+      <c r="L16">
+        <f>'Data Tables (M) w_cb_zip'!L6-'Data Tables (M) no zip'!L6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17">
+        <f>'Data Tables (M) w_cb_zip'!B7-'Data Tables (M) no zip'!B7</f>
+        <v/>
+      </c>
+      <c r="C17">
+        <f>'Data Tables (M) w_cb_zip'!C7-'Data Tables (M) no zip'!C7</f>
+        <v/>
+      </c>
+      <c r="D17">
+        <f>'Data Tables (M) w_cb_zip'!D7-'Data Tables (M) no zip'!D7</f>
+        <v/>
+      </c>
+      <c r="E17">
+        <f>'Data Tables (M) w_cb_zip'!E7-'Data Tables (M) no zip'!E7</f>
+        <v/>
+      </c>
+      <c r="F17">
+        <f>'Data Tables (M) w_cb_zip'!F7-'Data Tables (M) no zip'!F7</f>
+        <v/>
+      </c>
+      <c r="G17">
+        <f>'Data Tables (M) w_cb_zip'!G7-'Data Tables (M) no zip'!G7</f>
+        <v/>
+      </c>
+      <c r="H17">
+        <f>'Data Tables (M) w_cb_zip'!H7-'Data Tables (M) no zip'!H7</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>'Data Tables (M) w_cb_zip'!I7-'Data Tables (M) no zip'!I7</f>
+        <v/>
+      </c>
+      <c r="J17">
+        <f>'Data Tables (M) w_cb_zip'!J7-'Data Tables (M) no zip'!J7</f>
+        <v/>
+      </c>
+      <c r="K17">
+        <f>'Data Tables (M) w_cb_zip'!K7-'Data Tables (M) no zip'!K7</f>
+        <v/>
+      </c>
+      <c r="L17">
+        <f>'Data Tables (M) w_cb_zip'!L7-'Data Tables (M) no zip'!L7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18">
+        <f>'Data Tables (M) w_cb_zip'!B8-'Data Tables (M) no zip'!B8</f>
+        <v/>
+      </c>
+      <c r="C18">
+        <f>'Data Tables (M) w_cb_zip'!C8-'Data Tables (M) no zip'!C8</f>
+        <v/>
+      </c>
+      <c r="D18">
+        <f>'Data Tables (M) w_cb_zip'!D8-'Data Tables (M) no zip'!D8</f>
+        <v/>
+      </c>
+      <c r="E18">
+        <f>'Data Tables (M) w_cb_zip'!E8-'Data Tables (M) no zip'!E8</f>
+        <v/>
+      </c>
+      <c r="F18">
+        <f>'Data Tables (M) w_cb_zip'!F8-'Data Tables (M) no zip'!F8</f>
+        <v/>
+      </c>
+      <c r="G18">
+        <f>'Data Tables (M) w_cb_zip'!G8-'Data Tables (M) no zip'!G8</f>
+        <v/>
+      </c>
+      <c r="H18">
+        <f>'Data Tables (M) w_cb_zip'!H8-'Data Tables (M) no zip'!H8</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>'Data Tables (M) w_cb_zip'!I8-'Data Tables (M) no zip'!I8</f>
+        <v/>
+      </c>
+      <c r="J18">
+        <f>'Data Tables (M) w_cb_zip'!J8-'Data Tables (M) no zip'!J8</f>
+        <v/>
+      </c>
+      <c r="K18">
+        <f>'Data Tables (M) w_cb_zip'!K8-'Data Tables (M) no zip'!K8</f>
+        <v/>
+      </c>
+      <c r="L18">
+        <f>'Data Tables (M) w_cb_zip'!L8-'Data Tables (M) no zip'!L8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19">
+        <f>'Data Tables (M) w_cb_zip'!B9-'Data Tables (M) no zip'!B9</f>
+        <v/>
+      </c>
+      <c r="C19">
+        <f>'Data Tables (M) w_cb_zip'!C9-'Data Tables (M) no zip'!C9</f>
+        <v/>
+      </c>
+      <c r="D19">
+        <f>'Data Tables (M) w_cb_zip'!D9-'Data Tables (M) no zip'!D9</f>
+        <v/>
+      </c>
+      <c r="E19">
+        <f>'Data Tables (M) w_cb_zip'!E9-'Data Tables (M) no zip'!E9</f>
+        <v/>
+      </c>
+      <c r="F19">
+        <f>'Data Tables (M) w_cb_zip'!F9-'Data Tables (M) no zip'!F9</f>
+        <v/>
+      </c>
+      <c r="G19">
+        <f>'Data Tables (M) w_cb_zip'!G9-'Data Tables (M) no zip'!G9</f>
+        <v/>
+      </c>
+      <c r="H19">
+        <f>'Data Tables (M) w_cb_zip'!H9-'Data Tables (M) no zip'!H9</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>'Data Tables (M) w_cb_zip'!I9-'Data Tables (M) no zip'!I9</f>
+        <v/>
+      </c>
+      <c r="J19">
+        <f>'Data Tables (M) w_cb_zip'!J9-'Data Tables (M) no zip'!J9</f>
+        <v/>
+      </c>
+      <c r="K19">
+        <f>'Data Tables (M) w_cb_zip'!K9-'Data Tables (M) no zip'!K9</f>
+        <v/>
+      </c>
+      <c r="L19">
+        <f>'Data Tables (M) w_cb_zip'!L9-'Data Tables (M) no zip'!L9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20">
+        <f>'Data Tables (M) w_cb_zip'!B10-'Data Tables (M) no zip'!B10</f>
+        <v/>
+      </c>
+      <c r="C20">
+        <f>'Data Tables (M) w_cb_zip'!C10-'Data Tables (M) no zip'!C10</f>
+        <v/>
+      </c>
+      <c r="D20">
+        <f>'Data Tables (M) w_cb_zip'!D10-'Data Tables (M) no zip'!D10</f>
+        <v/>
+      </c>
+      <c r="E20">
+        <f>'Data Tables (M) w_cb_zip'!E10-'Data Tables (M) no zip'!E10</f>
+        <v/>
+      </c>
+      <c r="F20">
+        <f>'Data Tables (M) w_cb_zip'!F10-'Data Tables (M) no zip'!F10</f>
+        <v/>
+      </c>
+      <c r="G20">
+        <f>'Data Tables (M) w_cb_zip'!G10-'Data Tables (M) no zip'!G10</f>
+        <v/>
+      </c>
+      <c r="H20">
+        <f>'Data Tables (M) w_cb_zip'!H10-'Data Tables (M) no zip'!H10</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>'Data Tables (M) w_cb_zip'!I10-'Data Tables (M) no zip'!I10</f>
+        <v/>
+      </c>
+      <c r="J20">
+        <f>'Data Tables (M) w_cb_zip'!J10-'Data Tables (M) no zip'!J10</f>
+        <v/>
+      </c>
+      <c r="K20">
+        <f>'Data Tables (M) w_cb_zip'!K10-'Data Tables (M) no zip'!K10</f>
+        <v/>
+      </c>
+      <c r="L20">
+        <f>'Data Tables (M) w_cb_zip'!L10-'Data Tables (M) no zip'!L10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21">
+        <f>'Data Tables (M) w_cb_zip'!B11-'Data Tables (M) no zip'!B11</f>
+        <v/>
+      </c>
+      <c r="C21">
+        <f>'Data Tables (M) w_cb_zip'!C11-'Data Tables (M) no zip'!C11</f>
+        <v/>
+      </c>
+      <c r="D21">
+        <f>'Data Tables (M) w_cb_zip'!D11-'Data Tables (M) no zip'!D11</f>
+        <v/>
+      </c>
+      <c r="E21">
+        <f>'Data Tables (M) w_cb_zip'!E11-'Data Tables (M) no zip'!E11</f>
+        <v/>
+      </c>
+      <c r="F21">
+        <f>'Data Tables (M) w_cb_zip'!F11-'Data Tables (M) no zip'!F11</f>
+        <v/>
+      </c>
+      <c r="G21">
+        <f>'Data Tables (M) w_cb_zip'!G11-'Data Tables (M) no zip'!G11</f>
+        <v/>
+      </c>
+      <c r="H21">
+        <f>'Data Tables (M) w_cb_zip'!H11-'Data Tables (M) no zip'!H11</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>'Data Tables (M) w_cb_zip'!I11-'Data Tables (M) no zip'!I11</f>
+        <v/>
+      </c>
+      <c r="J21">
+        <f>'Data Tables (M) w_cb_zip'!J11-'Data Tables (M) no zip'!J11</f>
+        <v/>
+      </c>
+      <c r="K21">
+        <f>'Data Tables (M) w_cb_zip'!K11-'Data Tables (M) no zip'!K11</f>
+        <v/>
+      </c>
+      <c r="L21">
+        <f>'Data Tables (M) w_cb_zip'!L11-'Data Tables (M) no zip'!L11</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -700,147 +1772,97 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-03-01/2026-03-07</t>
+          <t>2026-05-31/2026-06-06</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>2026-03-08/2026-03-14</t>
+          <t>2026-06-07/2026-06-13</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-03-15/2026-03-21</t>
+          <t>2026-06-14/2026-06-20</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-03-22/2026-03-28</t>
+          <t>2026-06-21/2026-06-27</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-03-29/2026-04-04</t>
+          <t>2026-06-28/2026-07-04</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-04-05/2026-04-11</t>
+          <t>2026-07-05/2026-07-11</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-04-12/2026-04-18</t>
+          <t>2026-07-12/2026-07-18</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-04-19/2026-04-25</t>
+          <t>2026-07-19/2026-07-25</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-04-26/2026-05-02</t>
+          <t>2026-07-26/2026-08-01</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-03/2026-05-09</t>
+          <t>2026-08-02/2026-08-08</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-10/2026-05-16</t>
+          <t>2026-08-09/2026-08-15</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-05-17/2026-05-23</t>
+          <t>2026-08-16/2026-08-22</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-05-24/2026-05-30</t>
+          <t>2026-08-23/2026-08-29</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-05-31/2026-06-06</t>
+          <t>2026-08-30/2026-09-05</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-06-07/2026-06-13</t>
+          <t>2026-09-06/2026-09-12</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-06-14/2026-06-20</t>
+          <t>2026-09-13/2026-09-19</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-06-21/2026-06-27</t>
+          <t>2026-09-20/2026-09-26</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>2026-06-28/2026-07-04</t>
+          <t>2026-09-27/2026-10-03</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>2026-07-05/2026-07-11</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>2026-07-12/2026-07-18</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>2026-07-19/2026-07-25</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>2026-07-26/2026-08-01</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>2026-08-02/2026-08-08</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>2026-08-09/2026-08-15</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>2026-08-16/2026-08-22</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>2026-08-23/2026-08-29</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>2026-08-30/2026-09-05</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>2026-09-06/2026-09-12</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>2026-09-13/2026-09-19</t>
+          <t>2026-10-04/2026-10-10</t>
         </is>
       </c>
     </row>
@@ -851,91 +1873,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>134.5604309856327</v>
+        <v>136.3769169697765</v>
       </c>
       <c r="C2" t="n">
-        <v>134.5779375050316</v>
+        <v>136.4871710709409</v>
       </c>
       <c r="D2" t="n">
-        <v>134.7189061544075</v>
+        <v>137.1872162588645</v>
       </c>
       <c r="E2" t="n">
-        <v>135.0365116176407</v>
+        <v>137.1428366760989</v>
       </c>
       <c r="F2" t="n">
-        <v>134.9890345945214</v>
+        <v>137.8299723341297</v>
       </c>
       <c r="G2" t="n">
-        <v>135.2535635896063</v>
+        <v>137.2696870075733</v>
       </c>
       <c r="H2" t="n">
-        <v>134.9910830685765</v>
+        <v>137.3875426753543</v>
       </c>
       <c r="I2" t="n">
-        <v>135.7153366347619</v>
+        <v>137.0004567979578</v>
       </c>
       <c r="J2" t="n">
-        <v>136.5189509248592</v>
+        <v>137.7202308735054</v>
       </c>
       <c r="K2" t="n">
-        <v>136.467666297404</v>
+        <v>137.3392893270023</v>
       </c>
       <c r="L2" t="n">
-        <v>135.6865522182398</v>
+        <v>137.8644752992943</v>
       </c>
       <c r="M2" t="n">
-        <v>136.939193134382</v>
+        <v>137.3596019193337</v>
       </c>
       <c r="N2" t="n">
-        <v>136.2926431673899</v>
+        <v>137.4537927576926</v>
       </c>
       <c r="O2" t="n">
-        <v>136.3769169697765</v>
+        <v>137.5628664399206</v>
       </c>
       <c r="P2" t="n">
-        <v>136.4871710709409</v>
+        <v>137.2591876571248</v>
       </c>
       <c r="Q2" t="n">
-        <v>137.1872162588645</v>
+        <v>137.5506248615269</v>
       </c>
       <c r="R2" t="n">
-        <v>137.1428366760989</v>
+        <v>136.7945668951994</v>
       </c>
       <c r="S2" t="n">
-        <v>137.8299723341297</v>
+        <v>137.7385547792066</v>
       </c>
       <c r="T2" t="n">
-        <v>137.2696870075733</v>
-      </c>
-      <c r="U2" t="n">
-        <v>137.3875426753543</v>
-      </c>
-      <c r="V2" t="n">
-        <v>137.0004567979578</v>
-      </c>
-      <c r="W2" t="n">
-        <v>137.7202308735054</v>
-      </c>
-      <c r="X2" t="n">
-        <v>137.3392893270023</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>137.8644752992943</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>137.3608071623642</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>137.519419922114</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>137.5949343504855</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>137.2765830338531</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>137.4612039372404</v>
+        <v>137.813402288978</v>
       </c>
     </row>
     <row r="3">
@@ -945,91 +1937,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1128371612916794</v>
+        <v>-0.08670798084884268</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.438268763024098</v>
+        <v>-0.06404318494796257</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.5781489557388682</v>
+        <v>-0.5561507533783754</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4907208859036416</v>
+        <v>-0.06199918477398114</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4163346051206531</v>
+        <v>-0.1223021417754921</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.03955464343013659</v>
+        <v>0.1382983642251929</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2603304515904767</v>
+        <v>0.1158962312483709</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08957072496619389</v>
+        <v>0.4541363366376743</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3357501600719957</v>
+        <v>0.06508448327170413</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2773315007916324</v>
+        <v>0.3137234825882729</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6148758360910449</v>
+        <v>0.1275977298847124</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7512052518266898</v>
+        <v>0.5642515616557375</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2099464197166583</v>
+        <v>0.4008539910158504</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7395483498240765</v>
+        <v>0.2556539559541307</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5167102066655502</v>
+        <v>0.5566149023721607</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.051939364355462</v>
+        <v>0.9752757112285337</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.4929877103858757</v>
+        <v>0.8571389634806224</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5018413682082894</v>
+        <v>-0.09275252561525349</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3271680632845175</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-0.5005451176403994</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-0.1250414382457734</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-0.3823031788418234</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.254436116627005</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-0.2855456133790426</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.0753509679117883</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-0.1860743828638363</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-0.3108766397042473</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.03230159002629307</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.2332315850964051</v>
+        <v>1.514230331174787</v>
       </c>
     </row>
     <row r="4">
@@ -1039,91 +2001,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.259543259622068</v>
+        <v>3.963332965785394</v>
       </c>
       <c r="C4" t="n">
-        <v>1.359794043021511</v>
+        <v>4.230843173000186</v>
       </c>
       <c r="D4" t="n">
-        <v>1.667662658300501</v>
+        <v>3.899974718799932</v>
       </c>
       <c r="E4" t="n">
-        <v>1.900567885434507</v>
+        <v>4.897403872708026</v>
       </c>
       <c r="F4" t="n">
-        <v>2.414305081406356</v>
+        <v>4.333464735324456</v>
       </c>
       <c r="G4" t="n">
-        <v>2.38276335066755</v>
+        <v>4.079215440447669</v>
       </c>
       <c r="H4" t="n">
-        <v>2.87207162237852</v>
+        <v>4.022071865703817</v>
       </c>
       <c r="I4" t="n">
-        <v>2.614869504083102</v>
+        <v>3.157247112104061</v>
       </c>
       <c r="J4" t="n">
-        <v>3.812609316566847</v>
+        <v>3.483431083179653</v>
       </c>
       <c r="K4" t="n">
-        <v>3.707292408489872</v>
+        <v>3.036519699816549</v>
       </c>
       <c r="L4" t="n">
-        <v>3.44665191074496</v>
+        <v>3.671775564155406</v>
       </c>
       <c r="M4" t="n">
-        <v>3.567126338645887</v>
+        <v>3.567226048676129</v>
       </c>
       <c r="N4" t="n">
-        <v>4.496235065421107</v>
+        <v>3.885529033832466</v>
       </c>
       <c r="O4" t="n">
-        <v>3.94435125067836</v>
+        <v>3.266537178924036</v>
       </c>
       <c r="P4" t="n">
-        <v>4.213775518625501</v>
+        <v>3.146844492977051</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.880589075897163</v>
+        <v>2.710742497066468</v>
       </c>
       <c r="R4" t="n">
-        <v>4.881215806047438</v>
+        <v>2.82536534061009</v>
       </c>
       <c r="S4" t="n">
-        <v>4.32153109440354</v>
+        <v>1.709526920571117</v>
       </c>
       <c r="T4" t="n">
-        <v>4.065381870530694</v>
-      </c>
-      <c r="U4" t="n">
-        <v>4.004049102898515</v>
-      </c>
-      <c r="V4" t="n">
-        <v>3.143937785230215</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3.464262073744603</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.023998439548365</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>3.651022520697587</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.512872178819046</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.800442938811831</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>3.356430714703734</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.026996324036509</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.688342662641205</v>
+        <v>2.643894335876566</v>
       </c>
     </row>
     <row r="5">
@@ -1133,91 +2065,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.644519355697938</v>
+        <v>6.244339946715268</v>
       </c>
       <c r="C5" t="n">
-        <v>5.417109523204971</v>
+        <v>6.242989180681817</v>
       </c>
       <c r="D5" t="n">
-        <v>5.336899838516342</v>
+        <v>5.967034713487973</v>
       </c>
       <c r="E5" t="n">
-        <v>5.818572209781546</v>
+        <v>6.10430138370748</v>
       </c>
       <c r="F5" t="n">
-        <v>5.906341523563946</v>
+        <v>6.8144891330586</v>
       </c>
       <c r="G5" t="n">
-        <v>5.672823464806111</v>
+        <v>6.030332687329202</v>
       </c>
       <c r="H5" t="n">
-        <v>6.000339050413649</v>
+        <v>6.567728111418498</v>
       </c>
       <c r="I5" t="n">
-        <v>6.3540035274861</v>
+        <v>6.341203609470618</v>
       </c>
       <c r="J5" t="n">
-        <v>6.465652727202383</v>
+        <v>6.080086661123238</v>
       </c>
       <c r="K5" t="n">
-        <v>6.439216388517878</v>
+        <v>5.691283522854956</v>
       </c>
       <c r="L5" t="n">
-        <v>6.3552946793665</v>
+        <v>6.37908273367759</v>
       </c>
       <c r="M5" t="n">
-        <v>6.355292696404416</v>
+        <v>6.258774260988579</v>
       </c>
       <c r="N5" t="n">
-        <v>6.311442676123551</v>
+        <v>6.281405758221428</v>
       </c>
       <c r="O5" t="n">
-        <v>6.244339946715268</v>
+        <v>5.829493104724923</v>
       </c>
       <c r="P5" t="n">
-        <v>6.242989180681817</v>
+        <v>5.762670544632917</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.967034713487968</v>
+        <v>6.011637278639553</v>
       </c>
       <c r="R5" t="n">
-        <v>6.10430138370748</v>
+        <v>5.295445352239414</v>
       </c>
       <c r="S5" t="n">
-        <v>6.8144891330586</v>
+        <v>5.409750040614483</v>
       </c>
       <c r="T5" t="n">
-        <v>6.030332687329194</v>
-      </c>
-      <c r="U5" t="n">
-        <v>6.567728111418498</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6.341203609470618</v>
-      </c>
-      <c r="W5" t="n">
-        <v>6.080086661123241</v>
-      </c>
-      <c r="X5" t="n">
-        <v>5.691283522854956</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>6.379082733677587</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>6.232371287139952</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>6.281127619979269</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>5.890733679950617</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.7303922074188</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>6.431757844854843</v>
+        <v>5.972285025164799</v>
       </c>
     </row>
     <row r="6">
@@ -1227,91 +2129,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.629861600152719</v>
+        <v>1.860600213168589</v>
       </c>
       <c r="C6" t="n">
-        <v>1.553381866885359</v>
+        <v>1.782460024726735</v>
       </c>
       <c r="D6" t="n">
-        <v>1.787805777167024</v>
+        <v>1.801764739250849</v>
       </c>
       <c r="E6" t="n">
-        <v>1.791244046291852</v>
+        <v>2.140831858930344</v>
       </c>
       <c r="F6" t="n">
-        <v>1.694380991794107</v>
+        <v>2.193812629762514</v>
       </c>
       <c r="G6" t="n">
-        <v>1.667278357832026</v>
+        <v>1.879607243516968</v>
       </c>
       <c r="H6" t="n">
-        <v>1.433777536464584</v>
+        <v>1.724231727553024</v>
       </c>
       <c r="I6" t="n">
-        <v>1.542577217771107</v>
+        <v>1.662185175931949</v>
       </c>
       <c r="J6" t="n">
-        <v>1.765550519477232</v>
+        <v>2.033012048912933</v>
       </c>
       <c r="K6" t="n">
-        <v>1.971307930380207</v>
+        <v>1.595923885425471</v>
       </c>
       <c r="L6" t="n">
-        <v>1.599976535332507</v>
+        <v>1.902741439923062</v>
       </c>
       <c r="M6" t="n">
-        <v>2.004076609729814</v>
+        <v>1.720906339485452</v>
       </c>
       <c r="N6" t="n">
-        <v>2.037796780453788</v>
+        <v>1.74527965159217</v>
       </c>
       <c r="O6" t="n">
-        <v>1.860600213168585</v>
+        <v>1.781739970153719</v>
       </c>
       <c r="P6" t="n">
-        <v>1.782460024726733</v>
+        <v>1.476792913767652</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.801764739250846</v>
+        <v>1.81824983961319</v>
       </c>
       <c r="R6" t="n">
-        <v>2.140831858930341</v>
+        <v>1.323926752608874</v>
       </c>
       <c r="S6" t="n">
-        <v>2.193812629762514</v>
+        <v>1.678727251345103</v>
       </c>
       <c r="T6" t="n">
-        <v>1.879607243516966</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.724231727553024</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.662185175931949</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.033012048912933</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.595923885425469</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.902741439923062</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.730944541637672</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.748502670054186</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.80023728994588</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.429040339866881</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.733658648787693</v>
+        <v>1.911524554688351</v>
       </c>
     </row>
     <row r="7">
@@ -1321,91 +2193,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>143.1730211893658</v>
+        <v>148.3796517953527</v>
       </c>
       <c r="C7" t="n">
-        <v>142.3336690748075</v>
+        <v>148.7056499305091</v>
       </c>
       <c r="D7" t="n">
-        <v>142.8678014805443</v>
+        <v>148.2724897090178</v>
       </c>
       <c r="E7" t="n">
-        <v>144.0616418388722</v>
+        <v>150.2000143048307</v>
       </c>
       <c r="F7" t="n">
-        <v>144.7306322847472</v>
+        <v>151.1639001050138</v>
       </c>
       <c r="G7" t="n">
-        <v>144.9142330800786</v>
+        <v>149.2449649346973</v>
       </c>
       <c r="H7" t="n">
-        <v>145.0576354891677</v>
+        <v>149.8829179518311</v>
       </c>
       <c r="I7" t="n">
-        <v>146.1902386311612</v>
+        <v>148.5535615111218</v>
       </c>
       <c r="J7" t="n">
-        <v>148.27817405507</v>
+        <v>149.4140875731959</v>
       </c>
       <c r="K7" t="n">
-        <v>148.2155600439256</v>
+        <v>148.107606582353</v>
       </c>
       <c r="L7" t="n">
-        <v>146.6892235386327</v>
+        <v>149.9048514629542</v>
       </c>
       <c r="M7" t="n">
-        <v>147.9649320144552</v>
+        <v>149.4578755905982</v>
       </c>
       <c r="N7" t="n">
-        <v>148.9906273199708</v>
+        <v>149.7598298532697</v>
       </c>
       <c r="O7" t="n">
-        <v>147.7078297112704</v>
+        <v>148.6067285502486</v>
       </c>
       <c r="P7" t="n">
-        <v>148.2359152544169</v>
+        <v>148.3028167083898</v>
       </c>
       <c r="Q7" t="n">
-        <v>147.757315455138</v>
+        <v>149.0454505315432</v>
       </c>
       <c r="R7" t="n">
-        <v>149.7528377125583</v>
+        <v>147.1942356243194</v>
       </c>
       <c r="S7" t="n">
-        <v>150.7724272376601</v>
+        <v>146.4101994385285</v>
       </c>
       <c r="T7" t="n">
-        <v>148.7656649372706</v>
-      </c>
-      <c r="U7" t="n">
-        <v>149.248453840137</v>
-      </c>
-      <c r="V7" t="n">
-        <v>147.9610744093644</v>
-      </c>
-      <c r="W7" t="n">
-        <v>148.9475309016474</v>
-      </c>
-      <c r="X7" t="n">
-        <v>147.5269257228695</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>149.4709550762326</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>148.8994051025361</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>149.1671272255782</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>148.2947186624033</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>147.662966257221</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>147.397140312131</v>
+        <v>149.2157616181397</v>
       </c>
     </row>
     <row r="8">
@@ -1415,91 +2257,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26808842.22</v>
+        <v>16518116.51</v>
       </c>
       <c r="C8" t="n">
-        <v>24216184.26</v>
+        <v>18382664</v>
       </c>
       <c r="D8" t="n">
-        <v>22738839.63</v>
+        <v>17696771.35</v>
       </c>
       <c r="E8" t="n">
-        <v>23009188.67</v>
+        <v>18280560.81</v>
       </c>
       <c r="F8" t="n">
-        <v>20161572.45</v>
+        <v>15235894.33</v>
       </c>
       <c r="G8" t="n">
-        <v>18012071.24</v>
+        <v>13288046.4</v>
       </c>
       <c r="H8" t="n">
-        <v>17960297.72</v>
+        <v>14955864.38</v>
       </c>
       <c r="I8" t="n">
-        <v>17354570.6</v>
+        <v>14445556.33</v>
       </c>
       <c r="J8" t="n">
-        <v>15804446.5</v>
+        <v>14590541.69</v>
       </c>
       <c r="K8" t="n">
-        <v>17842306.87</v>
+        <v>13867492.61</v>
       </c>
       <c r="L8" t="n">
-        <v>16822819.55</v>
+        <v>12990570.21</v>
       </c>
       <c r="M8" t="n">
-        <v>17652040.04</v>
+        <v>12715759.94</v>
       </c>
       <c r="N8" t="n">
-        <v>21712230.49</v>
+        <v>14108815.44</v>
       </c>
       <c r="O8" t="n">
-        <v>16518116.51</v>
+        <v>12162464.36</v>
       </c>
       <c r="P8" t="n">
-        <v>18382664</v>
+        <v>11800477.59</v>
       </c>
       <c r="Q8" t="n">
-        <v>17696771.35</v>
+        <v>11072445.99</v>
       </c>
       <c r="R8" t="n">
-        <v>18280560.81</v>
+        <v>10479957.77</v>
       </c>
       <c r="S8" t="n">
-        <v>15235894.33</v>
+        <v>4860735.72</v>
       </c>
       <c r="T8" t="n">
-        <v>13288046.4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>14955864.38</v>
-      </c>
-      <c r="V8" t="n">
-        <v>14445556.33</v>
-      </c>
-      <c r="W8" t="n">
-        <v>14590541.69</v>
-      </c>
-      <c r="X8" t="n">
-        <v>13867492.61</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>12990570.21</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>12604081.71</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>13805307.74</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>11062219.13</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>9761064.550000001</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>4116371.66</v>
+        <v>468844.4600000001</v>
       </c>
     </row>
     <row r="9">
@@ -1509,91 +2321,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.45642305239309</v>
+        <v>1.418840030545178</v>
       </c>
       <c r="C9" t="n">
-        <v>1.471197701285302</v>
+        <v>1.418922486416291</v>
       </c>
       <c r="D9" t="n">
-        <v>1.476480632425605</v>
+        <v>1.435971182672165</v>
       </c>
       <c r="E9" t="n">
-        <v>1.445313917838496</v>
+        <v>1.427439828293471</v>
       </c>
       <c r="F9" t="n">
-        <v>1.439775966235079</v>
+        <v>1.384871193991648</v>
       </c>
       <c r="G9" t="n">
-        <v>1.454604895203864</v>
+        <v>1.432024471715291</v>
       </c>
       <c r="H9" t="n">
-        <v>1.433891906015484</v>
+        <v>1.399371201334476</v>
       </c>
       <c r="I9" t="n">
-        <v>1.41217757208886</v>
+        <v>1.412951986187142</v>
       </c>
       <c r="J9" t="n">
-        <v>1.405458453826353</v>
+        <v>1.428937442230339</v>
       </c>
       <c r="K9" t="n">
-        <v>1.407043625236373</v>
+        <v>1.45342152931905</v>
       </c>
       <c r="L9" t="n">
-        <v>1.412099502608141</v>
+        <v>1.410662701171431</v>
       </c>
       <c r="M9" t="n">
-        <v>1.412099622501298</v>
+        <v>1.41795950336543</v>
       </c>
       <c r="N9" t="n">
-        <v>1.414755854376158</v>
+        <v>1.416581126693936</v>
       </c>
       <c r="O9" t="n">
-        <v>1.418840030545178</v>
+        <v>1.444622526164379</v>
       </c>
       <c r="P9" t="n">
-        <v>1.418922486416291</v>
+        <v>1.448863389527736</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.435971182672166</v>
+        <v>1.433187895352998</v>
       </c>
       <c r="R9" t="n">
-        <v>1.427439828293471</v>
+        <v>1.479225890264058</v>
       </c>
       <c r="S9" t="n">
-        <v>1.384871193991648</v>
+        <v>1.471680850532846</v>
       </c>
       <c r="T9" t="n">
-        <v>1.432024471715291</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.399371201334476</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.412951986187142</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.428937442230338</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.45342152931905</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.410662701171431</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.419570976736918</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.416598050504109</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.440757664700206</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.45092085077335</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.407491500141197</v>
+        <v>1.435642991712506</v>
       </c>
     </row>
     <row r="10">
@@ -1603,91 +2385,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2267162628549612</v>
+        <v>0.2234199969547344</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2278088304730663</v>
+        <v>0.2245362853610466</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2244599174690425</v>
+        <v>0.2242605037249879</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2244107993386878</v>
+        <v>0.2194166877295665</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2257945572600842</v>
+        <v>0.2186598195748212</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2261817377452568</v>
+        <v>0.2231484679497576</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2295174637647917</v>
+        <v>0.2253681181778139</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2279631826032699</v>
+        <v>0.2262544974866864</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2247778497217538</v>
+        <v>0.2209569707298152</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2218384581374256</v>
+        <v>0.2272010873510647</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2271431923523927</v>
+        <v>0.2228179794296705</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2213703341467169</v>
+        <v>0.2254156237216364</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2208886174220887</v>
+        <v>0.2250674335486833</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2234199969547345</v>
+        <v>0.2245465718549469</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2245362853610467</v>
+        <v>0.2289029583747478</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2242605037249879</v>
+        <v>0.2240250022912401</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2194166877295665</v>
+        <v>0.2310867606770161</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2186598195748212</v>
+        <v>0.2260181821236414</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2231484679497576</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.2253681181778139</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.2262544974866864</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.2209569707298152</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.2272010873510647</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.2228179794296705</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.2252722208337475</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.2250213904277973</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0.2242823244293446</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.2295851380019017</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.2252334478744615</v>
+        <v>0.222692506361595</v>
       </c>
     </row>
   </sheetData>
